--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>894</v>
       </c>
       <c r="C2">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D2">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="E2">
         <v>1643</v>
@@ -405,10 +405,10 @@
         <v>921</v>
       </c>
       <c r="C3">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="D3">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="E3">
         <v>1651</v>
@@ -422,10 +422,10 @@
         <v>852</v>
       </c>
       <c r="C4">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="D4">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="E4">
         <v>1630</v>
@@ -490,13 +490,13 @@
         <v>858</v>
       </c>
       <c r="C8">
-        <v>1251</v>
+        <v>1262</v>
       </c>
       <c r="D8">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="E8">
-        <v>1621</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,10 +507,10 @@
         <v>969</v>
       </c>
       <c r="C9">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D9">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="E9">
         <v>1663</v>
@@ -578,7 +578,7 @@
         <v>1364</v>
       </c>
       <c r="D13">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="E13">
         <v>1662</v>
